--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486852_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486852_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. IKPEZE</t>
+          <t>A. LIBROIA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4576</v>
+        <v>4.8346</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3329</v>
+        <v>2.7472</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1247</v>
+        <v>2.0874</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2005</v>
+        <v>1.8858</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6781</v>
+        <v>-0.0614</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.8786</v>
+        <v>1.9472</v>
       </c>
       <c r="J2" t="n">
-        <v>1.6012</v>
+        <v>2.9872</v>
       </c>
       <c r="K2" t="n">
-        <v>1.4828</v>
+        <v>1.8561</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1184</v>
+        <v>1.1311</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.8017</v>
+        <v>-1.1014</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8047</v>
+        <v>-1.9175</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.997</v>
+        <v>0.8161</v>
       </c>
       <c r="P2" t="n">
-        <v>1.0267</v>
+        <v>1.6427</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.2321</v>
+        <v>-2.2588</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2588</v>
+        <v>3.9015</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5225</v>
+        <v>0.7168</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0725</v>
+        <v>1.1893</v>
       </c>
       <c r="U2" t="n">
-        <v>0.45</v>
+        <v>-0.4725</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1088</v>
+        <v>0.5893</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.1088</v>
+        <v>0.8295</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2177</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3739</v>
+        <v>3.7016</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0111</v>
+        <v>1.2203</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3628</v>
+        <v>2.4813</v>
       </c>
       <c r="G3" t="n">
         <v>0.2836</v>
@@ -688,13 +688,13 @@
         <v>2.4641</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4393</v>
+        <v>0.7671</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1122</v>
+        <v>0.3214</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3271</v>
+        <v>0.4457</v>
       </c>
       <c r="V3" t="n">
         <v>1.4189</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. LIBROIA</t>
+          <t>A. IKPEZE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0812</v>
+        <v>1.8581</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1123</v>
+        <v>1.0002</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9688</v>
+        <v>0.8579</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8858</v>
+        <v>-0.2005</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0614</v>
+        <v>0.6781</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9472</v>
+        <v>-0.8786</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9872</v>
+        <v>1.6012</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8561</v>
+        <v>1.4828</v>
       </c>
       <c r="L4" t="n">
-        <v>1.1311</v>
+        <v>0.1184</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1014</v>
+        <v>-1.8017</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.9175</v>
+        <v>-0.8047</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8161</v>
+        <v>-0.997</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6427</v>
+        <v>1.0267</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2588</v>
+        <v>-1.2321</v>
       </c>
       <c r="R4" t="n">
-        <v>3.9015</v>
+        <v>2.2588</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0367</v>
+        <v>0.923</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4457</v>
+        <v>0.7398</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5911</v>
+        <v>0.1832</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5893</v>
+        <v>0.1088</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8295</v>
+        <v>-0.1088</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2402</v>
+        <v>0.2177</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. SANCHEZ PERDIGUERO</t>
+          <t>O. NDOUR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9732</v>
+        <v>1.6147</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1782</v>
+        <v>1.9394</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.205</v>
+        <v>-0.3248</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7845</v>
+        <v>1.5072</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3243</v>
+        <v>0.3018</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4602</v>
+        <v>1.2054</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0172</v>
+        <v>2.922</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8988</v>
+        <v>1.5801</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1184</v>
+        <v>1.3418</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8017</v>
+        <v>-1.4147</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2231</v>
+        <v>-1.2783</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5786</v>
+        <v>-0.1364</v>
       </c>
       <c r="P5" t="n">
-        <v>1.2321</v>
+        <v>-2.4641</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0267</v>
+        <v>-5.1336</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2588</v>
+        <v>2.6694</v>
       </c>
       <c r="S5" t="n">
-        <v>2.7433</v>
+        <v>1.1527</v>
       </c>
       <c r="T5" t="n">
-        <v>3.1651</v>
+        <v>1.3133</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4218</v>
+        <v>-0.1606</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2177</v>
+        <v>1.4189</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0225</v>
+        <v>2.8377</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2402</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. NDOUR</t>
+          <t>A. SANCHEZ PERDIGUERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4341</v>
+        <v>1.395</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4625</v>
+        <v>1.5704</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0284</v>
+        <v>-0.1754</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5072</v>
+        <v>-0.7845</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3018</v>
+        <v>-0.3243</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2054</v>
+        <v>-0.4602</v>
       </c>
       <c r="J6" t="n">
-        <v>2.922</v>
+        <v>1.0172</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5801</v>
+        <v>0.8988</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3418</v>
+        <v>0.1184</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4147</v>
+        <v>-1.8017</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2783</v>
+        <v>-1.2231</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1364</v>
+        <v>-0.5786</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.4641</v>
+        <v>1.2321</v>
       </c>
       <c r="Q6" t="n">
-        <v>-5.1336</v>
+        <v>-1.0267</v>
       </c>
       <c r="R6" t="n">
-        <v>2.6694</v>
+        <v>2.2588</v>
       </c>
       <c r="S6" t="n">
-        <v>1.9721</v>
+        <v>1.1652</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8363</v>
+        <v>1.5574</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1358</v>
+        <v>-0.3922</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4189</v>
+        <v>-0.2177</v>
       </c>
       <c r="W6" t="n">
-        <v>2.8377</v>
+        <v>0.0225</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4189</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9659</v>
+        <v>0.9791</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2714</v>
+        <v>-0.1397</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2373</v>
+        <v>1.1187</v>
       </c>
       <c r="G7" t="n">
         <v>0.115</v>
@@ -1000,13 +1000,13 @@
         <v>1.8481</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0295</v>
+        <v>0.0427</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1045</v>
+        <v>0.2362</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.075</v>
+        <v>-0.1936</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4688</v>
+        <v>0.7422</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4571</v>
+        <v>-1.3913</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9259</v>
+        <v>2.1334</v>
       </c>
       <c r="G8" t="n">
         <v>-2.1645</v>
@@ -1078,13 +1078,13 @@
         <v>3.9015</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9906</v>
+        <v>1.264</v>
       </c>
       <c r="T8" t="n">
-        <v>1.5805</v>
+        <v>1.6464</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5899</v>
+        <v>-0.3824</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1552</v>
+        <v>-0.2706</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1703</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3254</v>
+        <v>-1.2661</v>
       </c>
       <c r="G9" t="n">
         <v>-2.1819</v>
@@ -1156,13 +1156,13 @@
         <v>2.8748</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1848</v>
+        <v>-0.3003</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9804</v>
+        <v>-0.1551</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2045</v>
+        <v>-0.1452</v>
       </c>
       <c r="V9" t="n">
         <v>-0.4579</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6994</v>
+        <v>-0.5373</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.163</v>
+        <v>-1.0899</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4636</v>
+        <v>0.5525</v>
       </c>
       <c r="G10" t="n">
         <v>0.5607</v>
@@ -1234,13 +1234,13 @@
         <v>2.4641</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.5989</v>
+        <v>-0.4368</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5192</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0797</v>
+        <v>-0.9907</v>
       </c>
       <c r="V10" t="n">
         <v>2.0082</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6967</v>
+        <v>-2.4966</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.002</v>
+        <v>-1.8315</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6948</v>
+        <v>-0.6651</v>
       </c>
       <c r="G11" t="n">
         <v>-1.961</v>
@@ -1312,13 +1312,13 @@
         <v>0.8214</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5304</v>
+        <v>-0.3303</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3952</v>
+        <v>-0.2248</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1352</v>
+        <v>-0.1055</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.0093</v>
+        <v>-3.6387</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3117</v>
+        <v>-2.9707</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6976</v>
+        <v>-0.668</v>
       </c>
       <c r="G12" t="n">
         <v>-3.0066</v>
@@ -1390,13 +1390,13 @@
         <v>1.2321</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5304</v>
+        <v>-0.1598</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.527</v>
+        <v>-0.186</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0034</v>
+        <v>0.0262</v>
       </c>
       <c r="V12" t="n">
         <v>0.3491</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.194099999999999</v>
+        <v>8.182100000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>1.0621</v>
+        <v>2.0499</v>
       </c>
       <c r="F13" t="n">
-        <v>6.1319</v>
+        <v>6.1318</v>
       </c>
       <c r="G13" t="n">
         <v>-5.9467</v>
@@ -1459,7 +1459,7 @@
         <v>-3.5751</v>
       </c>
       <c r="P13" t="n">
-        <v>4.1069</v>
+        <v>4.106900000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-22.5878</v>
@@ -1468,16 +1468,16 @@
         <v>26.6946</v>
       </c>
       <c r="S13" t="n">
-        <v>3.816099999999999</v>
+        <v>4.8043</v>
       </c>
       <c r="T13" t="n">
-        <v>6.0036</v>
+        <v>6.991799999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.1877</v>
+        <v>-2.1876</v>
       </c>
       <c r="V13" t="n">
-        <v>5.217600000000001</v>
+        <v>5.217599999999999</v>
       </c>
       <c r="W13" t="n">
         <v>7.3796</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2049</v>
+        <v>5.0312</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2284</v>
+        <v>2.856</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9764</v>
+        <v>2.1752</v>
       </c>
       <c r="G14" t="n">
         <v>3.216</v>
@@ -1546,13 +1546,13 @@
         <v>3.0801</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.6264</v>
+        <v>-0.8</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8486</v>
+        <v>-0.221</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7778</v>
+        <v>-0.579</v>
       </c>
       <c r="V14" t="n">
         <v>1.5885</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9545</v>
+        <v>0.7749</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3966</v>
+        <v>0.1874</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5579</v>
+        <v>0.5875</v>
       </c>
       <c r="G15" t="n">
         <v>2.3587</v>
@@ -1624,13 +1624,13 @@
         <v>1.6427</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3646</v>
+        <v>0.185</v>
       </c>
       <c r="T15" t="n">
-        <v>0.368</v>
+        <v>0.1588</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0034</v>
+        <v>0.0262</v>
       </c>
       <c r="V15" t="n">
         <v>-1.3581</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. CUELLAR GARCIA</t>
+          <t>J. SÁNCHEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2525</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7286</v>
+        <v>-1.5427</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4761</v>
+        <v>1.6243</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6878</v>
+        <v>0.9999</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8697</v>
+        <v>1.2133</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5576</v>
+        <v>-0.2134</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3832</v>
+        <v>1.925</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0156</v>
+        <v>2.7676</v>
       </c>
       <c r="L16" t="n">
-        <v>2.3676</v>
+        <v>-0.8425</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.6954</v>
+        <v>-0.9251</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.8854</v>
+        <v>-1.5543</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0.6291</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4107</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.6694</v>
+        <v>-3.6962</v>
       </c>
       <c r="R16" t="n">
-        <v>3.0801</v>
+        <v>3.4908</v>
       </c>
       <c r="S16" t="n">
-        <v>0.494</v>
+        <v>-0.5996</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7746</v>
+        <v>-0.0118</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2806</v>
+        <v>-0.5878</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.34</v>
+        <v>-0.1134</v>
       </c>
       <c r="W16" t="n">
         <v>0.2402</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.5803</v>
+        <v>-0.3536</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2859</v>
+        <v>-0.2266</v>
       </c>
       <c r="E17" t="n">
         <v>1.2912</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.577</v>
+        <v>-1.5178</v>
       </c>
       <c r="G17" t="n">
         <v>1.8152</v>
@@ -1780,13 +1780,13 @@
         <v>1.6427</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6424</v>
+        <v>-0.5831</v>
       </c>
       <c r="T17" t="n">
         <v>0.0386</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.681</v>
+        <v>-0.6217</v>
       </c>
       <c r="V17" t="n">
         <v>-0.6374</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. MORALES ROS</t>
+          <t>D. CUELLAR GARCIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7092000000000001</v>
+        <v>-0.2619</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.633</v>
+        <v>1.5194</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9238</v>
+        <v>-1.7813</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7158</v>
+        <v>0.6878</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1294</v>
+        <v>-0.8697</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8452</v>
+        <v>1.5576</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0091</v>
+        <v>3.3832</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0706</v>
+        <v>1.0156</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.0797</v>
+        <v>2.3676</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7067</v>
+        <v>-2.6954</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9412</v>
+        <v>-1.8854</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2345</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="P18" t="n">
         <v>0.4107</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.4641</v>
+        <v>-2.6694</v>
       </c>
       <c r="R18" t="n">
-        <v>2.8748</v>
+        <v>3.0801</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.055</v>
+        <v>-0.0203</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5384</v>
+        <v>0.5654</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5933</v>
+        <v>-0.5857</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3491</v>
+        <v>-1.34</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6982</v>
+        <v>0.2402</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3491</v>
+        <v>-1.5803</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. SÁNCHEZ</t>
+          <t>A. MORALES ROS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2416</v>
+        <v>-0.9428</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3795</v>
+        <v>-2.9468</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1379</v>
+        <v>2.004</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9999</v>
+        <v>-0.7158</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2133</v>
+        <v>0.1294</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2134</v>
+        <v>-0.8452</v>
       </c>
       <c r="J19" t="n">
-        <v>1.925</v>
+        <v>-0.0091</v>
       </c>
       <c r="K19" t="n">
-        <v>2.7676</v>
+        <v>1.0706</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.8425</v>
+        <v>-1.0797</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9251</v>
+        <v>-0.7067</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.5543</v>
+        <v>-0.9412</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6291</v>
+        <v>0.2345</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2053</v>
+        <v>0.4107</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.6962</v>
+        <v>-2.4641</v>
       </c>
       <c r="R19" t="n">
-        <v>3.4908</v>
+        <v>2.8748</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.9228</v>
+        <v>-0.2886</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8486</v>
+        <v>0.2246</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.0742</v>
+        <v>-0.5132</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1134</v>
+        <v>-0.3491</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2402</v>
+        <v>-0.6982</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3536</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. JACKSON</t>
+          <t>P. SALO BLAYA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8193</v>
+        <v>-2.4558</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0415</v>
+        <v>-0.4696</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7778</v>
+        <v>-1.9862</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3931</v>
+        <v>-0.1797</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.12</v>
+        <v>0.0518</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5131</v>
+        <v>-0.2314</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2683</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5713</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>0.697</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8753</v>
+        <v>-0.8415</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6913</v>
+        <v>-0.6101</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1839</v>
+        <v>-0.2314</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.0534</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.5175</v>
+        <v>-1.2321</v>
       </c>
       <c r="R20" t="n">
-        <v>2.4641</v>
+        <v>1.0267</v>
       </c>
       <c r="S20" t="n">
-        <v>1.8538</v>
+        <v>-0.5386</v>
       </c>
       <c r="T20" t="n">
-        <v>2.9675</v>
+        <v>0.1006</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.1137</v>
+        <v>-0.6392</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.0127</v>
+        <v>-1.5322</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.2529</v>
+        <v>-1.5322</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. SALO BLAYA</t>
+          <t>D. JACKSON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5046</v>
+        <v>-2.9612</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2604</v>
+        <v>-1.6105</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2443</v>
+        <v>-1.3507</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1797</v>
+        <v>0.3931</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0518</v>
+        <v>-0.12</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2314</v>
+        <v>0.5131</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6618000000000001</v>
+        <v>1.2683</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.5713</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.697</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8415</v>
+        <v>-0.8753</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6101</v>
+        <v>-0.6913</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2314</v>
+        <v>-0.1839</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.2053</v>
+        <v>-2.0534</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.2321</v>
+        <v>-4.5175</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0267</v>
+        <v>2.4641</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5874</v>
+        <v>0.7119</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3098</v>
+        <v>1.3985</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8972</v>
+        <v>-0.6866</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.5322</v>
+        <v>-2.0127</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.5322</v>
+        <v>-2.2529</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.0452</v>
+        <v>-4.8388</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.4624</v>
+        <v>-5.4164</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4173</v>
+        <v>0.5776</v>
       </c>
       <c r="G22" t="n">
         <v>-2.6286</v>
@@ -2170,13 +2170,13 @@
         <v>3.2855</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6945</v>
+        <v>-0.4881</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1121</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5824</v>
+        <v>-0.4221</v>
       </c>
       <c r="V22" t="n">
         <v>0.5368000000000001</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.1939</v>
+        <v>-5.799399999999999</v>
       </c>
       <c r="E23" t="n">
         <v>-6.132</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0619</v>
+        <v>0.3325999999999995</v>
       </c>
       <c r="G23" t="n">
         <v>5.9466</v>
@@ -2218,7 +2218,7 @@
         <v>3.6322</v>
       </c>
       <c r="I23" t="n">
-        <v>2.3145</v>
+        <v>2.314500000000001</v>
       </c>
       <c r="J23" t="n">
         <v>16.2127</v>
@@ -2227,7 +2227,7 @@
         <v>12.6377</v>
       </c>
       <c r="L23" t="n">
-        <v>3.575199999999999</v>
+        <v>3.5752</v>
       </c>
       <c r="M23" t="n">
         <v>-10.2662</v>
@@ -2248,13 +2248,13 @@
         <v>22.5875</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.8161</v>
+        <v>-2.4214</v>
       </c>
       <c r="T23" t="n">
         <v>2.1876</v>
       </c>
       <c r="U23" t="n">
-        <v>-6.0036</v>
+        <v>-4.609100000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-5.2176</v>
@@ -2263,7 +2263,7 @@
         <v>2.1619</v>
       </c>
       <c r="X23" t="n">
-        <v>-7.3797</v>
+        <v>-7.379700000000001</v>
       </c>
     </row>
   </sheetData>
